--- a/site/Microsoft-Entra-ID-to-Workday-User-Photo-Sync/headings.xlsx
+++ b/site/Microsoft-Entra-ID-to-Workday-User-Photo-Sync/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -485,73 +485,73 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Prerequisites</t>
+          <t>Key Functions</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>h_01J6RM7PH3DX54S93ABHZ8J2X8</t>
+          <t>h_01KKTJHV1NPMMJHQCX7RPKXRCC</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Microsoft-Entra-ID-to-Workday-User-Photo-Sync/#h_01J6RM7PH3DX54S93ABHZ8J2X8</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Microsoft-Entra-ID-to-Workday-User-Photo-Sync/#h_01KKTJHV1NPMMJHQCX7RPKXRCC</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Integration Setup</t>
+          <t>Prerequisites</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>h_01KEXYT4S6PBGE446BGJJST3YJ</t>
+          <t>h_01J6RM7PH3DX54S93ABHZ8J2X8</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Microsoft-Entra-ID-to-Workday-User-Photo-Sync/#h_01KEXYT4S6PBGE446BGJJST3YJ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Microsoft-Entra-ID-to-Workday-User-Photo-Sync/#h_01J6RM7PH3DX54S93ABHZ8J2X8</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Create Integration</t>
+          <t>Integration Setup</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>h_01KEXYT4S7MBFETFZYMR9QKS0M</t>
+          <t>h_01KEXYT4S6PBGE446BGJJST3YJ</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Microsoft-Entra-ID-to-Workday-User-Photo-Sync/#h_01KEXYT4S7MBFETFZYMR9QKS0M</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Microsoft-Entra-ID-to-Workday-User-Photo-Sync/#h_01KEXYT4S6PBGE446BGJJST3YJ</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Create Integration</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -561,41 +561,41 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>h_01KEXYT4SB88DN4JBNV7SJKRSV</t>
+          <t>h_01KEXYT4S7MBFETFZYMR9QKS0M</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Microsoft-Entra-ID-to-Workday-User-Photo-Sync/#h_01KEXYT4SB88DN4JBNV7SJKRSV</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Microsoft-Entra-ID-to-Workday-User-Photo-Sync/#h_01KEXYT4S7MBFETFZYMR9QKS0M</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Applications</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>h_01KEXYT4SCB0P407JTJS4H9AYE</t>
+          <t>h_01KEXYT4SB88DN4JBNV7SJKRSV</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Microsoft-Entra-ID-to-Workday-User-Photo-Sync/#h_01KEXYT4SCB0P407JTJS4H9AYE</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Microsoft-Entra-ID-to-Workday-User-Photo-Sync/#h_01KEXYT4SB88DN4JBNV7SJKRSV</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Parameters</t>
+          <t>Applications</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -605,19 +605,19 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>h_01KEXZA87A280KAVD4N7YTWTXY</t>
+          <t>h_01KEXYT4SCB0P407JTJS4H9AYE</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Microsoft-Entra-ID-to-Workday-User-Photo-Sync/#h_01KEXZA87A280KAVD4N7YTWTXY</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Microsoft-Entra-ID-to-Workday-User-Photo-Sync/#h_01KEXYT4SCB0P407JTJS4H9AYE</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Integration Features</t>
+          <t>Parameters</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -627,63 +627,63 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>h_01KEXZRH1Q7SDB2TMJ59K10QMY</t>
+          <t>h_01KEXZA87A280KAVD4N7YTWTXY</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Microsoft-Entra-ID-to-Workday-User-Photo-Sync/#h_01KEXZRH1Q7SDB2TMJ59K10QMY</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Microsoft-Entra-ID-to-Workday-User-Photo-Sync/#h_01KEXZA87A280KAVD4N7YTWTXY</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>General Settings</t>
+          <t>Integration Features</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>h_01KEXZVYQPPTTTJJTT6X3K7JMH</t>
+          <t>h_01KEXZRH1Q7SDB2TMJ59K10QMY</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Microsoft-Entra-ID-to-Workday-User-Photo-Sync/#h_01KEXZVYQPPTTTJJTT6X3K7JMH</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Microsoft-Entra-ID-to-Workday-User-Photo-Sync/#h_01KEXZRH1Q7SDB2TMJ59K10QMY</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Correlation Settings</t>
+          <t>General Settings</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>h_01KEY00G6AJXRDF7143ZTPMVYW</t>
+          <t>h_01KKTJVYPS7DQW756BWNQ7AND4</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Microsoft-Entra-ID-to-Workday-User-Photo-Sync/#h_01KEY00G6AJXRDF7143ZTPMVYW</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Microsoft-Entra-ID-to-Workday-User-Photo-Sync/#h_01KKTJVYPS7DQW756BWNQ7AND4</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Entra User Settings</t>
+          <t>Correlation Settings</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -693,19 +693,19 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>h_01KEY2EN0RDN0TDQEF74DWKZGT</t>
+          <t>h_01KEY00G6AJXRDF7143ZTPMVYW</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Microsoft-Entra-ID-to-Workday-User-Photo-Sync/#h_01KEY2EN0RDN0TDQEF74DWKZGT</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Microsoft-Entra-ID-to-Workday-User-Photo-Sync/#h_01KEY00G6AJXRDF7143ZTPMVYW</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Manage Users</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -715,56 +715,760 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01KEY0VRP1KKTGMPFD1W1SNRDV</t>
+          <t>h_01KKTKFXVHDSGS9R72DEX43SBG</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Microsoft-Entra-ID-to-Workday-User-Photo-Sync/#h_01KEY0VRP1KKTGMPFD1W1SNRDV</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Microsoft-Entra-ID-to-Workday-User-Photo-Sync/#h_01KKTKFXVHDSGS9R72DEX43SBG</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Create Users</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KEY0VRP28DFNKTTNRZ36WYVZ</t>
+          <t>h_01KKTQPDV9ZEPSTN07YWBASMDZ</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Microsoft-Entra-ID-to-Workday-User-Photo-Sync/#h_01KEY0VRP28DFNKTTNRZ36WYVZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Microsoft-Entra-ID-to-Workday-User-Photo-Sync/#h_01KKTQPDV9ZEPSTN07YWBASMDZ</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>Update User</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>h_01KKTQTTYP770MQKS2WEBRE0RY</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Microsoft-Entra-ID-to-Workday-User-Photo-Sync/#h_01KKTQTTYP770MQKS2WEBRE0RY</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Terminate User</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>h_01KKTKFXVP5S0S3BM7P7SQBR7H</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Microsoft-Entra-ID-to-Workday-User-Photo-Sync/#h_01KKTKFXVP5S0S3BM7P7SQBR7H</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Debug Mode</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>h_01KKTQ3T1G3FEBN68DWJEHJK84</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Microsoft-Entra-ID-to-Workday-User-Photo-Sync/#h_01KKTQ3T1G3FEBN68DWJEHJK84</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Debug Settings</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>h_01KKTQ3ZR8MGKVBN6P677Q6F6C</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Microsoft-Entra-ID-to-Workday-User-Photo-Sync/#h_01KKTQ3ZR8MGKVBN6P677Q6F6C</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Account Provisioning</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>h_01KKTQ7D2TEDFYM9RWSSEQ556S</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Microsoft-Entra-ID-to-Workday-User-Photo-Sync/#h_01KKTQ7D2TEDFYM9RWSSEQ556S</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Password Settings</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>h_01KKTQGQ325C2FTKG7J66S9VVX</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Microsoft-Entra-ID-to-Workday-User-Photo-Sync/#h_01KKTQGQ325C2FTKG7J66S9VVX</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Domain Name</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>h_01KKTQGQ35HGC81DVSMS89YCY7</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Microsoft-Entra-ID-to-Workday-User-Photo-Sync/#h_01KKTQGQ35HGC81DVSMS89YCY7</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Generate UserPrincipalName (UPN)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>h_01KKTQGQ366H3XZC070KTNPSBM</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Microsoft-Entra-ID-to-Workday-User-Photo-Sync/#h_01KKTQGQ366H3XZC070KTNPSBM</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Generate Email</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>h_01KKTQGQ379VJERBMHAP5M9XXS</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Microsoft-Entra-ID-to-Workday-User-Photo-Sync/#h_01KKTQGQ379VJERBMHAP5M9XXS</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Write Back for Email</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>h_01KKTR7CZEZWTJ8BHWP2PGS8YX</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Microsoft-Entra-ID-to-Workday-User-Photo-Sync/#h_01KKTR7CZEZWTJ8BHWP2PGS8YX</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Email Configuration</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>h_01KKTR7CZFPDBZPNK11WAY00D6</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Microsoft-Entra-ID-to-Workday-User-Photo-Sync/#h_01KKTR7CZFPDBZPNK11WAY00D6</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Photo Sync</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>h_01KKTS1SPRGNJC94JXMDVBM0E0</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Microsoft-Entra-ID-to-Workday-User-Photo-Sync/#h_01KKTS1SPRGNJC94JXMDVBM0E0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Photo Sync Settings</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>h_01KKTS1SPR8CKZPC40GMRPJ6MJ</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Microsoft-Entra-ID-to-Workday-User-Photo-Sync/#h_01KKTS1SPR8CKZPC40GMRPJ6MJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Time Aware LCM</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>h_01KKTS90XB8ZXJREQZQXX9HMNX</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Microsoft-Entra-ID-to-Workday-User-Photo-Sync/#h_01KKTS90XB8ZXJREQZQXX9HMNX</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Time Aware Settings</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>h_01KKTS90XC6G7SG8GPJM8B8KHD</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Microsoft-Entra-ID-to-Workday-User-Photo-Sync/#h_01KKTS90XC6G7SG8GPJM8B8KHD</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Onboarding Schedule Settings</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>h_01KKTSDHH1QGVEJJ6XVDKZF627</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Microsoft-Entra-ID-to-Workday-User-Photo-Sync/#h_01KKTSDHH1QGVEJJ6XVDKZF627</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Report Settings</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>h_01KJBZXKQVBA7MT6TF4FN456B4</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Microsoft-Entra-ID-to-Workday-User-Photo-Sync/#h_01KJBZXKQVBA7MT6TF4FN456B4</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Report Settings</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>h_01KKTT3ST7A0HBSW0NZF10TKYS</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Microsoft-Entra-ID-to-Workday-User-Photo-Sync/#h_01KKTT3ST7A0HBSW0NZF10TKYS</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Log Settings</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>h_01KKTTV50MEJRNTBPHG6QS1H62</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Microsoft-Entra-ID-to-Workday-User-Photo-Sync/#h_01KKTTV50MEJRNTBPHG6QS1H62</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Log Configuration</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>h_01KKTTV50N8HJ91SWXFVVDRRVA</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Microsoft-Entra-ID-to-Workday-User-Photo-Sync/#h_01KKTTV50N8HJ91SWXFVVDRRVA</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Notifications</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>h_01KKTVMZ6KAC39A3SS0YNDTVC8</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Microsoft-Entra-ID-to-Workday-User-Photo-Sync/#h_01KKTVMZ6KAC39A3SS0YNDTVC8</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Notification Settings</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>h_01KKTVPXVNCW5163JW89SS6E3B</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Microsoft-Entra-ID-to-Workday-User-Photo-Sync/#h_01KKTVPXVNCW5163JW89SS6E3B</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Success Notification Settings</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>h_01KKTVMZ6MCCGM52GCHN9HT70D</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Microsoft-Entra-ID-to-Workday-User-Photo-Sync/#h_01KKTVMZ6MCCGM52GCHN9HT70D</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Failure Notification Settings</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>h_01KKTVMZ6PB4FG3M60K73ZVPH8</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Microsoft-Entra-ID-to-Workday-User-Photo-Sync/#h_01KKTVMZ6PB4FG3M60K73ZVPH8</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Notification Report Settings</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>h_01KKTVMZ6R6GM9N0C0QYCB7HQ0</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Microsoft-Entra-ID-to-Workday-User-Photo-Sync/#h_01KKTVMZ6R6GM9N0C0QYCB7HQ0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Log Insights</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>h_01KKTW0YB3BJ089MQ0SFMRGYYF</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Microsoft-Entra-ID-to-Workday-User-Photo-Sync/#h_01KKTW0YB3BJ089MQ0SFMRGYYF</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Log Insights Settings</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>h_01KKTW0YB45P6DZFV8KBPF96A1</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Microsoft-Entra-ID-to-Workday-User-Photo-Sync/#h_01KKTW0YB45P6DZFV8KBPF96A1</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Attribute Mapper</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>h_01KKTWC785YZM4J6DH0F2ZKEQ6</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Microsoft-Entra-ID-to-Workday-User-Photo-Sync/#h_01KKTWC785YZM4J6DH0F2ZKEQ6</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>h_01KEY0VRP28DFNKTTNRZ36WYVZ</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Microsoft-Entra-ID-to-Workday-User-Photo-Sync/#h_01KEY0VRP28DFNKTTNRZ36WYVZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
           <t>Execute Integration</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>H3</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
         <is>
           <t>h_01KEY0VRP38CCXNPB165EJ6C27</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Microsoft-Entra-ID-to-Workday-User-Photo-Sync/#h_01KEY0VRP38CCXNPB165EJ6C27</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Additional Options</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>h_01KKTWEXSDDR5TJX9R40F5KEXN</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Microsoft-Entra-ID-to-Workday-User-Photo-Sync/#h_01KKTWEXSDDR5TJX9R40F5KEXN</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Update the Integration to the Latest Version</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>h_01KKTWEXSMAEMXKQCXGS6FWJHZ</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Microsoft-Entra-ID-to-Workday-User-Photo-Sync/#h_01KKTWEXSMAEMXKQCXGS6FWJHZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Upgrade an Integration</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>h_01KKTWEXSP9XTFJDSS42HRY4KA</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Microsoft-Entra-ID-to-Workday-User-Photo-Sync/#h_01KKTWEXSP9XTFJDSS42HRY4KA</t>
         </is>
       </c>
     </row>
